--- a/htr-Mapping-CDA-FHIR/ig/StructureDefinition-PatientUsager.xlsx
+++ b/htr-Mapping-CDA-FHIR/ig/StructureDefinition-PatientUsager.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-23T10:50:09+00:00</t>
+    <t>2025-05-23T12:29:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
